--- a/results/02_taxa_assemblage/MRT_Method/ModelC_Weighted/tables/site_eval_heldout.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelC_Weighted/tables/site_eval_heldout.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,49 +508,49 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>GL1</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Uncertain</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
       <c r="E2" t="n">
-        <v>3.9624</v>
+        <v>0.4</v>
       </c>
       <c r="F2" t="n">
-        <v>5.75</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>17.11</v>
+        <v>26.89</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7096774193548387</v>
+        <v>1.611842946668372</v>
       </c>
       <c r="I2" t="n">
-        <v>2.47</v>
+        <v>1.07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0602349469938161</v>
+        <v>0.7415967700971651</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7218422142045615</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2179228388016222</v>
+        <v>0.2584032299028349</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7218422142045615</v>
+        <v>0.7415967700971651</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5039193754029393</v>
+        <v>0.4831935401943302</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -561,11 +561,11 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -576,195 +576,36 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8288</v>
+        <v>4.3</v>
       </c>
       <c r="F3" t="n">
-        <v>11.76</v>
+        <v>8.91</v>
       </c>
       <c r="G3" t="n">
-        <v>20.62</v>
+        <v>21.15</v>
       </c>
       <c r="H3" t="n">
-        <v>1.023255813953488</v>
+        <v>1.520124887150165</v>
       </c>
       <c r="I3" t="n">
-        <v>1.55</v>
+        <v>0.601560297020399</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3580866825579639</v>
+        <v>0.7415967700971651</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06135728663996221</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.580556030802074</v>
+        <v>0.2584032299028349</v>
       </c>
       <c r="M3" t="n">
-        <v>0.580556030802074</v>
+        <v>0.7415967700971651</v>
       </c>
       <c r="N3" t="n">
-        <v>0.22246934824411</v>
+        <v>0.4831935401943302</v>
       </c>
       <c r="O3" t="inlineStr">
-        <is>
-          <t>Held-out</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Uncertain</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="G4" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.433404487688642</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.41342143147169</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.0602349469938161</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.7218422142045615</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.2179228388016222</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.7218422142045615</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.5039193754029393</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Held-out</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>S18</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Uncertain</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.62995516333357</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.50490599353894</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.0602349469938161</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.7218422142045615</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.2179228388016222</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.7218422142045615</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.5039193754029393</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Held-out</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Uncertain</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="G6" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.652212487523566</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.50636152676643</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.0602349469938161</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.7218422142045615</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.2179228388016222</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.7218422142045615</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.5039193754029393</v>
-      </c>
-      <c r="O6" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>

--- a/results/02_taxa_assemblage/MRT_Method/ModelC_Weighted/tables/site_eval_heldout.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelC_Weighted/tables/site_eval_heldout.xlsx
@@ -538,19 +538,19 @@
         <v>1.07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7415967700971651</v>
+        <v>0.6641892707670098</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.1137756944456308</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2584032299028349</v>
+        <v>0.2220350347873594</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7415967700971651</v>
+        <v>0.6641892707670098</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4831935401943302</v>
+        <v>0.4421542359796504</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -591,19 +591,19 @@
         <v>0.601560297020399</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7415967700971651</v>
+        <v>0.6641892707670098</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.1137756944456308</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2584032299028349</v>
+        <v>0.2220350347873594</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7415967700971651</v>
+        <v>0.6641892707670098</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4831935401943302</v>
+        <v>0.4421542359796504</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
